--- a/app/reports/combined_leave_report.xlsx
+++ b/app/reports/combined_leave_report.xlsx
@@ -32,12 +32,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -58,13 +68,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -572,11 +584,11 @@
           <t>app/uploads/sick_documents/Assignment 4 Final Project - Due Nov 26 (4).pdf</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>10</v>
+      <c r="M2" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -634,6 +646,180 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antonette</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>robinsonantonette2005@gmial.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>45264</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>vacation</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Antonette</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>robinsonantonette2005@gmial.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>45264</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>45997</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antonette</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>robinsonantonette2005@gmial.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fortnightly</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>45264</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>sick</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>45997</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>app/uploads/sick_documents/Assignment 4 Final Project - Due Nov 26 (4).pdf</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
     </row>
